--- a/Realistic_ER_Estimate/NTh/aggregate_Mumberes_results.xlsx
+++ b/Realistic_ER_Estimate/NTh/aggregate_Mumberes_results.xlsx
@@ -425,342 +425,854 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Maize</t>
+          <t>Maize - SOC Baseline (tCO2e/ha)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Maize - SOC Project (tCO2e/ha)</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maize - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Potato - SOC Baseline (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Potato - SOC Project (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Potato - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>412.4225681749645</v>
+      </c>
+      <c r="B2" t="n">
+        <v>412.4592013991095</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>412.4225681749645</v>
+      </c>
+      <c r="E2" t="n">
+        <v>412.4592013991095</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>354.2759089417121</v>
+      </c>
+      <c r="B3" t="n">
+        <v>412.4591982535782</v>
+      </c>
+      <c r="C3" t="n">
         <v>58.14665608772108</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
+        <v>347.2662986074387</v>
+      </c>
+      <c r="E3" t="n">
+        <v>412.4591982535782</v>
+      </c>
+      <c r="F3" t="n">
         <v>65.15626642199447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>323.7174160389758</v>
+      </c>
+      <c r="B4" t="n">
+        <v>412.4591953887187</v>
+      </c>
+      <c r="C4" t="n">
         <v>30.55849003787675</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
+        <v>312.9931379424456</v>
+      </c>
+      <c r="E4" t="n">
+        <v>412.4591953887187</v>
+      </c>
+      <c r="F4" t="n">
         <v>34.27315780013357</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>304.5229995041359</v>
+      </c>
+      <c r="B5" t="n">
+        <v>412.4591927794866</v>
+      </c>
+      <c r="C5" t="n">
         <v>19.19441392560782</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
+        <v>291.4171406908738</v>
+      </c>
+      <c r="E5" t="n">
+        <v>412.4591927794866</v>
+      </c>
+      <c r="F5" t="n">
         <v>21.5759946423397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>291.4020365269054</v>
+      </c>
+      <c r="B6" t="n">
+        <v>412.4591904030731</v>
+      </c>
+      <c r="C6" t="n">
         <v>13.12096060081704</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
+        <v>276.6089724389892</v>
+      </c>
+      <c r="E6" t="n">
+        <v>412.4591904030731</v>
+      </c>
+      <c r="F6" t="n">
         <v>14.80816587547114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>281.6155677102716</v>
+      </c>
+      <c r="B7" t="n">
+        <v>412.4591882387035</v>
+      </c>
+      <c r="C7" t="n">
         <v>9.786466652264133</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
+        <v>265.5013644893854</v>
+      </c>
+      <c r="E7" t="n">
+        <v>412.4591882387035</v>
+      </c>
+      <c r="F7" t="n">
         <v>11.10760578523421</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>273.7285073150951</v>
+      </c>
+      <c r="B8" t="n">
+        <v>412.4591862674579</v>
+      </c>
+      <c r="C8" t="n">
         <v>7.887058423931028</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
+        <v>256.4892066214658</v>
+      </c>
+      <c r="E8" t="n">
+        <v>412.4591862674579</v>
+      </c>
+      <c r="F8" t="n">
         <v>9.012155896673983</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>266.9813389034582</v>
+      </c>
+      <c r="B9" t="n">
+        <v>412.459184472104</v>
+      </c>
+      <c r="C9" t="n">
         <v>6.747166616283039</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
+        <v>248.7246741043075</v>
+      </c>
+      <c r="E9" t="n">
+        <v>412.459184472104</v>
+      </c>
+      <c r="F9" t="n">
         <v>7.764530721804491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>260.967534036824</v>
+      </c>
+      <c r="B10" t="n">
+        <v>412.459182836947</v>
+      </c>
+      <c r="C10" t="n">
         <v>6.01380323147708</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
+        <v>241.7554031711209</v>
+      </c>
+      <c r="E10" t="n">
+        <v>412.459182836947</v>
+      </c>
+      <c r="F10" t="n">
         <v>6.969269298029502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>255.4660248455268</v>
+      </c>
+      <c r="B11" t="n">
+        <v>412.459181347693</v>
+      </c>
+      <c r="C11" t="n">
         <v>5.501507702043146</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
+        <v>235.3366380663781</v>
+      </c>
+      <c r="E11" t="n">
+        <v>412.459181347693</v>
+      </c>
+      <c r="F11" t="n">
         <v>6.418763615488785</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>250.3536179458573</v>
+      </c>
+      <c r="B12" t="n">
+        <v>412.459179991323</v>
+      </c>
+      <c r="C12" t="n">
         <v>5.112405543299535</v>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
+        <v>229.3330552737947</v>
+      </c>
+      <c r="E12" t="n">
+        <v>412.459179991323</v>
+      </c>
+      <c r="F12" t="n">
         <v>6.003581436213405</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>245.5590199507909</v>
+      </c>
+      <c r="B13" t="n">
+        <v>412.4591787559802</v>
+      </c>
+      <c r="C13" t="n">
         <v>4.794596759723494</v>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
+        <v>223.6672542337805</v>
+      </c>
+      <c r="E13" t="n">
+        <v>412.4591787559802</v>
+      </c>
+      <c r="F13" t="n">
         <v>5.665799804671366</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>241.038642383849</v>
+      </c>
+      <c r="B14" t="n">
+        <v>412.4591776308653</v>
+      </c>
+      <c r="C14" t="n">
         <v>4.520376441827129</v>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
+        <v>218.2926651318078</v>
+      </c>
+      <c r="E14" t="n">
+        <v>412.4591776308653</v>
+      </c>
+      <c r="F14" t="n">
         <v>5.374587976857867</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>236.7638422676473</v>
+      </c>
+      <c r="B15" t="n">
+        <v>412.4591766061428</v>
+      </c>
+      <c r="C15" t="n">
         <v>4.274799091479053</v>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
+        <v>213.179272541727</v>
+      </c>
+      <c r="E15" t="n">
+        <v>412.4591766061428</v>
+      </c>
+      <c r="F15" t="n">
         <v>5.113391565358119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>232.7141787601996</v>
+      </c>
+      <c r="B16" t="n">
+        <v>412.4591756728548</v>
+      </c>
+      <c r="C16" t="n">
         <v>4.049662574159797</v>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
+        <v>208.3060783922676</v>
+      </c>
+      <c r="E16" t="n">
+        <v>412.4591756728548</v>
+      </c>
+      <c r="F16" t="n">
         <v>4.873193216171515</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>228.8738387345159</v>
+      </c>
+      <c r="B17" t="n">
+        <v>412.4591748228428</v>
+      </c>
+      <c r="C17" t="n">
         <v>3.840339175671735</v>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
+        <v>203.6571131792326</v>
+      </c>
+      <c r="E17" t="n">
+        <v>412.4591748228428</v>
+      </c>
+      <c r="F17" t="n">
         <v>4.648964363023012</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>225.2297333087488</v>
+      </c>
+      <c r="B18" t="n">
+        <v>412.4591740486765</v>
+      </c>
+      <c r="C18" t="n">
         <v>3.644104651600804</v>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
+        <v>199.2193170775808</v>
+      </c>
+      <c r="E18" t="n">
+        <v>412.4591740486765</v>
+      </c>
+      <c r="F18" t="n">
         <v>4.437795327485527</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>221.7704764038374</v>
+      </c>
+      <c r="B19" t="n">
+        <v>412.4591733435878</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.459256199822681</v>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
+        <v>194.981407397133</v>
+      </c>
+      <c r="E19" t="n">
+        <v>412.4591733435878</v>
+      </c>
+      <c r="F19" t="n">
         <v>4.237908975359109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>218.4858295605426</v>
+      </c>
+      <c r="B20" t="n">
+        <v>412.4591727014135</v>
+      </c>
+      <c r="C20" t="n">
         <v>3.284646201120495</v>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
+        <v>190.9332669400285</v>
+      </c>
+      <c r="E20" t="n">
+        <v>412.4591727014135</v>
+      </c>
+      <c r="F20" t="n">
         <v>4.048139814930077</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>215.3663937792921</v>
+      </c>
+      <c r="B21" t="n">
+        <v>412.4591721165394</v>
+      </c>
+      <c r="C21" t="n">
         <v>3.119435196376429</v>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
+        <v>187.0656079462252</v>
+      </c>
+      <c r="E21" t="n">
+        <v>412.4591721165394</v>
+      </c>
+      <c r="F21" t="n">
         <v>3.867658408929278</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>212.4034327086337</v>
+      </c>
+      <c r="B22" t="n">
+        <v>412.4591715838529</v>
+      </c>
+      <c r="C22" t="n">
         <v>2.962960537971881</v>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
+        <v>183.3697822651181</v>
+      </c>
+      <c r="E22" t="n">
+        <v>412.4591715838529</v>
+      </c>
+      <c r="F22" t="n">
         <v>3.695825148420662</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>209.5887661016506</v>
+      </c>
+      <c r="B23" t="n">
+        <v>412.4591710986974</v>
+      </c>
+      <c r="C23" t="n">
         <v>2.814666121827557</v>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
+        <v>179.8376694914121</v>
+      </c>
+      <c r="E23" t="n">
+        <v>412.4591710986974</v>
+      </c>
+      <c r="F23" t="n">
         <v>3.532112288550403</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>206.9147012490717</v>
+      </c>
+      <c r="B24" t="n">
+        <v>412.4591706568314</v>
+      </c>
+      <c r="C24" t="n">
         <v>2.674064410712882</v>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
+        <v>176.4616070100499</v>
+      </c>
+      <c r="E24" t="n">
+        <v>412.4591706568314</v>
+      </c>
+      <c r="F24" t="n">
         <v>3.376062039496224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>204.3739852853353</v>
+      </c>
+      <c r="B25" t="n">
+        <v>412.4591702543926</v>
+      </c>
+      <c r="C25" t="n">
         <v>2.54071556129764</v>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
+        <v>173.2343428772391</v>
+      </c>
+      <c r="E25" t="n">
+        <v>412.4591702543926</v>
+      </c>
+      <c r="F25" t="n">
         <v>3.227263730372025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>201.959769279766</v>
+      </c>
+      <c r="B26" t="n">
+        <v>412.459169887863</v>
+      </c>
+      <c r="C26" t="n">
         <v>2.414215639039677</v>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
+        <v>170.1490014228748</v>
+      </c>
+      <c r="E26" t="n">
+        <v>412.459169887863</v>
+      </c>
+      <c r="F26" t="n">
         <v>3.085341087834654</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>199.6655792587737</v>
+      </c>
+      <c r="B27" t="n">
+        <v>412.4591695540381</v>
+      </c>
+      <c r="C27" t="n">
         <v>2.294189687167446</v>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
+        <v>167.1990561879298</v>
+      </c>
+      <c r="E27" t="n">
+        <v>412.4591695540381</v>
+      </c>
+      <c r="F27" t="n">
         <v>2.949944901120171</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>197.4852915435519</v>
+      </c>
+      <c r="B28" t="n">
+        <v>412.4591692500003</v>
+      </c>
+      <c r="C28" t="n">
         <v>2.180287411184035</v>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
+        <v>164.3783073082334</v>
+      </c>
+      <c r="E28" t="n">
+        <v>412.4591692500003</v>
+      </c>
+      <c r="F28" t="n">
         <v>2.820748575658575</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>195.4131109734905</v>
+      </c>
+      <c r="B29" t="n">
+        <v>412.4591689730912</v>
+      </c>
+      <c r="C29" t="n">
         <v>2.072180293152286</v>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
+        <v>161.6808617774838</v>
+      </c>
+      <c r="E29" t="n">
+        <v>412.4591689730912</v>
+      </c>
+      <c r="F29" t="n">
         <v>2.697445253840437</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>193.4435512154267</v>
+      </c>
+      <c r="B30" t="n">
+        <v>412.4591687208902</v>
+      </c>
+      <c r="C30" t="n">
         <v>1.9695595058628</v>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
+        <v>159.1011157230335</v>
+      </c>
+      <c r="E30" t="n">
+        <v>412.4591687208902</v>
+      </c>
+      <c r="F30" t="n">
         <v>2.579745802249386</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>191.5714166951168</v>
+      </c>
+      <c r="B31" t="n">
+        <v>412.4591684911929</v>
+      </c>
+      <c r="C31" t="n">
         <v>1.872134290612616</v>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
+        <v>156.6337382009734</v>
+      </c>
+      <c r="E31" t="n">
+        <v>412.4591684911929</v>
+      </c>
+      <c r="F31" t="n">
         <v>2.467377292362831</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>189.7917858682709</v>
+      </c>
+      <c r="B32" t="n">
+        <v>412.459168281991</v>
+      </c>
+      <c r="C32" t="n">
         <v>1.779630617643974</v>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
+        <v>154.2736562168633</v>
+      </c>
+      <c r="E32" t="n">
+        <v>412.459168281991</v>
+      </c>
+      <c r="F32" t="n">
         <v>2.360081774908172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>188.0999956471718</v>
+      </c>
+      <c r="B33" t="n">
+        <v>412.4591680914561</v>
+      </c>
+      <c r="C33" t="n">
         <v>1.691790030564178</v>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
+        <v>152.0160407866584</v>
+      </c>
+      <c r="E33" t="n">
+        <v>412.4591680914561</v>
+      </c>
+      <c r="F33" t="n">
         <v>2.257615239669889</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>186.4916268538599</v>
+      </c>
+      <c r="B34" t="n">
+        <v>412.4591679179221</v>
+      </c>
+      <c r="C34" t="n">
         <v>1.608368619777901</v>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
+        <v>149.8562939119847</v>
+      </c>
+      <c r="E34" t="n">
+        <v>412.4591679179221</v>
+      </c>
+      <c r="F34" t="n">
         <v>2.159746701139738</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>184.9624906024806</v>
+      </c>
+      <c r="B35" t="n">
+        <v>412.4591677598725</v>
+      </c>
+      <c r="C35" t="n">
         <v>1.529136093329664</v>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
+        <v>147.7900363776543</v>
+      </c>
+      <c r="E35" t="n">
+        <v>412.4591677598725</v>
+      </c>
+      <c r="F35" t="n">
         <v>2.066257376280817</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>183.5086155324505</v>
+      </c>
+      <c r="B36" t="n">
+        <v>412.4591676159257</v>
+      </c>
+      <c r="C36" t="n">
         <v>1.453874926083226</v>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
+        <v>145.8130962991927</v>
+      </c>
+      <c r="E36" t="n">
+        <v>412.4591676159257</v>
+      </c>
+      <c r="F36" t="n">
         <v>1.976939934514779</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>182.1262358263099</v>
+      </c>
+      <c r="B37" t="n">
+        <v>412.459167484823</v>
+      </c>
+      <c r="C37" t="n">
         <v>1.382379575038101</v>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
+        <v>143.9214983605249</v>
+      </c>
+      <c r="E37" t="n">
+        <v>412.459167484823</v>
+      </c>
+      <c r="F37" t="n">
         <v>1.891597807565224</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>180.8117799545278</v>
+      </c>
+      <c r="B38" t="n">
+        <v>412.4591673654184</v>
+      </c>
+      <c r="C38" t="n">
         <v>1.314455752377384</v>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
+        <v>142.1114536902237</v>
+      </c>
+      <c r="E38" t="n">
+        <v>412.4591673654184</v>
+      </c>
+      <c r="F38" t="n">
         <v>1.810044550896525</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>179.5618600957468</v>
+      </c>
+      <c r="B39" t="n">
+        <v>412.4591672566678</v>
+      </c>
+      <c r="C39" t="n">
         <v>1.249919750030476</v>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
+        <v>140.3793503306397</v>
+      </c>
+      <c r="E39" t="n">
+        <v>412.4591672566678</v>
+      </c>
+      <c r="F39" t="n">
         <v>1.73210325083348</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>178.373262185852</v>
+      </c>
+      <c r="B40" t="n">
+        <v>412.4591671576212</v>
+      </c>
+      <c r="C40" t="n">
         <v>1.188597810848175</v>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
+        <v>138.7217442587884</v>
+      </c>
+      <c r="E40" t="n">
+        <v>412.4591671576212</v>
+      </c>
+      <c r="F40" t="n">
         <v>1.65760597280467</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>177.2429365533251</v>
+      </c>
+      <c r="B41" t="n">
+        <v>412.4591670674124</v>
+      </c>
+      <c r="C41" t="n">
         <v>1.130325542318104</v>
       </c>
-      <c r="B41" t="n">
+      <c r="D41" t="n">
+        <v>137.1353509215738</v>
+      </c>
+      <c r="E41" t="n">
+        <v>412.4591670674124</v>
+      </c>
+      <c r="F41" t="n">
         <v>1.586393247005778</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>176.1679891018399</v>
+      </c>
+      <c r="B42" t="n">
+        <v>412.4591669852527</v>
+      </c>
+      <c r="C42" t="n">
         <v>1.074947369325457</v>
       </c>
-      <c r="B42" t="n">
+      <c r="D42" t="n">
+        <v>135.6170372510759</v>
+      </c>
+      <c r="E42" t="n">
+        <v>412.4591669852527</v>
+      </c>
+      <c r="F42" t="n">
         <v>1.518313588338122</v>
       </c>
     </row>
